--- a/data/intermediate/niger_kegg.xlsx
+++ b/data/intermediate/niger_kegg.xlsx
@@ -677,6 +677,9 @@
     <t xml:space="preserve">Proton (energy metabolism)</t>
   </si>
   <si>
+    <t xml:space="preserve">energy_C00080</t>
+  </si>
+  <si>
     <t xml:space="preserve">Water</t>
   </si>
   <si>
@@ -945,9 +948,6 @@
   </si>
   <si>
     <t xml:space="preserve">C00183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proton</t>
   </si>
   <si>
     <t xml:space="preserve">L-Rhamnonic acid</t>
@@ -2437,7 +2437,7 @@
         <v>220</v>
       </c>
       <c r="B138" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="139">
@@ -2450,189 +2450,189 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B140" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B141" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B142" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B143" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B144" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B145" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B146" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B147" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B148" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B149" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B150"/>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B151" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B152" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B153" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B154" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B155" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B156" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B157" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B158" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B159" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B160" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B161" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B162" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B163" t="s">
         <v>177</v>
@@ -2640,39 +2640,39 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B164" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B166" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B167" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B168" t="s">
         <v>177</v>
@@ -2680,77 +2680,77 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B169" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B170" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B171" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B172" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B173" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B174" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B175" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B176"/>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B177" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B178" t="s">
         <v>177</v>
@@ -2758,221 +2758,219 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B179" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B180" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B181" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B182" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B183" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B184" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B185" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B186" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B187" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B188" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B189"/>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B190" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B191" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B192" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B193" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B194" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B195" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B196" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B197" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B198" t="s">
-        <v>219</v>
+        <v>313</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B199" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B200" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B201" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>318</v>
-      </c>
-      <c r="B202" t="s">
-        <v>319</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="B202"/>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B203"/>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B204"/>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B205"/>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B206"/>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B207"/>
     </row>
@@ -2984,187 +2982,181 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>325</v>
-      </c>
-      <c r="B209"/>
+        <v>326</v>
+      </c>
+      <c r="B209" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B210" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>328</v>
+        <v>34</v>
       </c>
       <c r="B211" t="s">
-        <v>329</v>
+        <v>35</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B212" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>26</v>
+        <v>330</v>
       </c>
       <c r="B213" t="s">
-        <v>27</v>
+        <v>331</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B214" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>332</v>
+        <v>293</v>
       </c>
       <c r="B215" t="s">
-        <v>333</v>
+        <v>294</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="B216" t="s">
-        <v>293</v>
+        <v>335</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B217" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B218" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>338</v>
+        <v>243</v>
       </c>
       <c r="B219" t="s">
-        <v>339</v>
+        <v>244</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B220" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>244</v>
-      </c>
-      <c r="B221" t="s">
-        <v>245</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="B221"/>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B222"/>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>341</v>
-      </c>
-      <c r="B223"/>
+        <v>342</v>
+      </c>
+      <c r="B223" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B224" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B225" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B226" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B227" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B228" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B229" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B230" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B231" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="s">
-        <v>358</v>
-      </c>
-      <c r="B232" t="s">
         <v>359</v>
       </c>
     </row>
